--- a/Excel/EntryConfig@s.xlsx
+++ b/Excel/EntryConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20880" windowHeight="12240"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="EntryConfig" sheetId="1" r:id="rId1"/>
@@ -1156,7 +1156,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>1002</v>
+        <v>1011</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -1179,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="4">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H7" s="4">
         <v>1</v>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="4">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="H8" s="4">
         <v>2000</v>
@@ -1271,7 +1271,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>1002</v>
+        <v>1011</v>
       </c>
       <c r="H11" s="4">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="4">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="H13" s="4">
         <v>3000</v>
@@ -1386,7 +1386,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>1002</v>
+        <v>1011</v>
       </c>
       <c r="H16" s="4">
         <v>4</v>
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="G17" s="4">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="H17" s="4">
         <v>4</v>
@@ -1432,7 +1432,7 @@
         <v>3</v>
       </c>
       <c r="G18" s="4">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="H18" s="4">
         <v>4000</v>

--- a/Excel/EntryConfig@s.xlsx
+++ b/Excel/EntryConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="EntryConfig" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <t>词条评分</t>
   </si>
   <si>
-    <t>属性类型</t>
+    <t>属性类型（需要有推导属性才行）</t>
   </si>
   <si>
     <t>属性值最小范围</t>
@@ -1294,7 +1294,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="4">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H12" s="4">
         <v>2</v>
@@ -1432,7 +1432,7 @@
         <v>3</v>
       </c>
       <c r="G18" s="4">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H18" s="4">
         <v>4000</v>
